--- a/XmlData/Datas/dialog.xlsx
+++ b/XmlData/Datas/dialog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362A381D-9118-4946-A8DF-F874F2D8A0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4363995C-2F95-430C-9727-BAC92FDBB545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-1210" windowWidth="25820" windowHeight="15500" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>##</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,12 +59,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>dialogType</t>
-  </si>
-  <si>
-    <t>content</t>
-  </si>
-  <si>
     <t>0left1right</t>
   </si>
   <si>
@@ -129,9 +119,6 @@
     <t>Last time we were here was university time.</t>
   </si>
   <si>
-    <t>Time flies, at that time you still was not willing to admit you crushed on me.</t>
-  </si>
-  <si>
     <t>Shut up…</t>
   </si>
   <si>
@@ -139,6 +126,21 @@
   </si>
   <si>
     <t>When do you think the economy will be better?</t>
+  </si>
+  <si>
+    <t>DialogBoxType</t>
+  </si>
+  <si>
+    <t>DialogContent</t>
+  </si>
+  <si>
+    <t>list,DialogData</t>
+  </si>
+  <si>
+    <t>*dialogData</t>
+  </si>
+  <si>
+    <t>Time flies, at that time you even don't know how to talk to a girl.</t>
   </si>
 </sst>
 </file>
@@ -162,20 +164,35 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -184,9 +201,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,10 +528,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="77.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -517,14 +543,12 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
@@ -534,49 +558,50 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -584,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -592,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -600,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -612,25 +637,25 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -638,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -646,15 +671,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -662,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -670,74 +695,74 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21">
         <v>3</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -748,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -756,10 +781,22 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
